--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.159" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.159" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.159.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.159.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0159.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0159.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -871,7 +871,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.159" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.159" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y70"/>
+  <dimension ref="A1:Y72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€” See Orders of 1850, under which pleadings need not</t>
+          <t>L76: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”The folio consists of 100 words.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]152</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]152</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 152</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L18: symbol-only separator/garbage line :: .5 0</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]152</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,12 +664,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œspecial applications for summary reference, under</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Office Copyâ€¢</t>
+          <t>L39: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Office Copy•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -677,7 +681,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: #</t>
+          <t>L18: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -719,12 +723,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L126: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”See Orders of 1850,under which pleadings need not</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -736,7 +740,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L99: symbol-only separator/garbage line :: 0 6</t>
+          <t>L86: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -762,12 +766,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -778,14 +782,10 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L145: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”It is submitted that, although it has not been done</t>
-        </is>
-      </c>
+          <t>L145: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: .</t>
+          <t>L99: symbol-only separator/garbage line :: 0 6</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -835,16 +835,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L166: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€” See Orders of 1850, under which pleadings need not</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -854,7 +846,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 13</t>
+          <t>L116: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -890,11 +882,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œspecial applications for summary reference, under</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -905,7 +893,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L118: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -952,7 +940,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: I</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -999,7 +987,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: %</t>
+          <t>L124: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1021,12 +1009,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1044,7 +1032,11 @@
           <t>L26: isolated marker/symbol line :: 5</t>
         </is>
       </c>
-      <c r="O10" s="1" t="inlineStr"/>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>L126: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr"/>
@@ -1069,7 +1061,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1107,12 +1099,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1435,7 +1427,7 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 1</t>
+          <t>L76: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr"/>
@@ -1466,7 +1458,7 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 0</t>
+          <t>L77: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr"/>
@@ -1497,7 +1489,7 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 1</t>
+          <t>L78: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr"/>
@@ -1528,7 +1520,7 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 0</t>
+          <t>L81: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr"/>
@@ -1559,7 +1551,7 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: Â·</t>
+          <t>L82: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr"/>
@@ -1590,7 +1582,7 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 0</t>
+          <t>L87: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr"/>
@@ -1621,7 +1613,7 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 6</t>
+          <t>L88: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr"/>
@@ -1652,7 +1644,7 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 1</t>
+          <t>L89: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr"/>
@@ -1683,7 +1675,7 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 5</t>
+          <t>L90: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr"/>
@@ -1714,7 +1706,7 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 0</t>
+          <t>L93: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr"/>
@@ -1745,7 +1737,7 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: 5</t>
+          <t>L94: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr"/>
@@ -1776,7 +1768,7 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 0</t>
+          <t>L97: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr"/>
@@ -1807,7 +1799,7 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L98: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr"/>
@@ -1838,7 +1830,7 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: 5</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -1869,7 +1861,7 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 0</t>
+          <t>L104: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr"/>
@@ -1900,7 +1892,7 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: 2</t>
+          <t>L105: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr"/>
@@ -1931,7 +1923,7 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L109: isolated marker/symbol line :: 6</t>
+          <t>L108: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr"/>
@@ -1962,7 +1954,7 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: 0</t>
+          <t>L109: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -1993,7 +1985,7 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L113: isolated marker/symbol line :: 4</t>
+          <t>L112: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2024,7 +2016,7 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 5</t>
+          <t>L113: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2055,7 +2047,7 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: 0</t>
+          <t>L116: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2086,7 +2078,7 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L120: symbol-only separator/garbage line :: 1 3</t>
+          <t>L117: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2117,7 +2109,7 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L123: isolated marker/symbol line :: 1</t>
+          <t>L120: symbol-only separator/garbage line :: 1 3</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2148,7 +2140,7 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 3</t>
+          <t>L123: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2179,7 +2171,7 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: 1</t>
+          <t>L124: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2210,7 +2202,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L128: isolated marker/symbol line :: 0</t>
+          <t>L126: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2241,7 +2233,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: 1</t>
+          <t>L127: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2272,7 +2264,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: 0</t>
+          <t>L128: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2303,7 +2295,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L134: isolated marker/symbol line :: Â·</t>
+          <t>L130: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2334,7 +2326,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L135: isolated marker/symbol line :: 0</t>
+          <t>L131: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2365,7 +2357,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L136: isolated marker/symbol line :: 6</t>
+          <t>L134: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2396,7 +2388,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L138: isolated marker/symbol line :: 5</t>
+          <t>L135: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2427,7 +2419,7 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: 0</t>
+          <t>L136: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -2458,7 +2450,7 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L141: isolated marker/symbol line :: 5</t>
+          <t>L138: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -2489,7 +2481,7 @@
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L142: isolated marker/symbol line :: 0</t>
+          <t>L139: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -2520,7 +2512,7 @@
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L145: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L141: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -2551,7 +2543,7 @@
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: 5</t>
+          <t>L142: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -2582,7 +2574,7 @@
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L147: isolated marker/symbol line :: 0</t>
+          <t>L145: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -2613,7 +2605,7 @@
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L149: isolated marker/symbol line :: 2</t>
+          <t>L146: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -2644,7 +2636,7 @@
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: 6</t>
+          <t>L147: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -2675,7 +2667,7 @@
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L152: isolated marker/symbol line :: 0</t>
+          <t>L149: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -2706,7 +2698,7 @@
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L153: isolated marker/symbol line :: 4</t>
+          <t>L150: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -2737,7 +2729,7 @@
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L155: isolated marker/symbol line :: 5</t>
+          <t>L152: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -2768,7 +2760,7 @@
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L156: isolated marker/symbol line :: 0</t>
+          <t>L153: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -2799,7 +2791,7 @@
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L159: symbol-only separator/garbage line :: 1 3</t>
+          <t>L155: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -2830,7 +2822,7 @@
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L164: isolated marker/symbol line :: 10</t>
+          <t>L156: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -2861,7 +2853,7 @@
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L165: isolated marker/symbol line :: 0</t>
+          <t>L159: symbol-only separator/garbage line :: 1 3</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -2892,7 +2884,7 @@
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L170: symbol-only separator/garbage line :: . 25</t>
+          <t>L164: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -2923,7 +2915,7 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L171: isolated marker/symbol line :: 0</t>
+          <t>L165: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -2954,7 +2946,7 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L179: isolated marker/symbol line :: 2</t>
+          <t>L170: symbol-only separator/garbage line :: . 25</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -2985,7 +2977,7 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L180: isolated marker/symbol line :: 2</t>
+          <t>L171: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3000,6 +2992,68 @@
       <c r="X70" s="1" t="inlineStr"/>
       <c r="Y70" s="1" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr"/>
+      <c r="B71" s="1" t="inlineStr"/>
+      <c r="C71" s="1" t="inlineStr"/>
+      <c r="D71" s="1" t="inlineStr"/>
+      <c r="E71" s="1" t="inlineStr"/>
+      <c r="F71" s="1" t="inlineStr"/>
+      <c r="G71" s="1" t="inlineStr"/>
+      <c r="H71" s="1" t="inlineStr"/>
+      <c r="I71" s="1" t="inlineStr"/>
+      <c r="J71" s="1" t="inlineStr"/>
+      <c r="K71" s="1" t="inlineStr"/>
+      <c r="L71" s="1" t="inlineStr"/>
+      <c r="M71" s="1" t="inlineStr"/>
+      <c r="N71" s="1" t="inlineStr">
+        <is>
+          <t>L179: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O71" s="1" t="inlineStr"/>
+      <c r="P71" s="1" t="inlineStr"/>
+      <c r="Q71" s="1" t="inlineStr"/>
+      <c r="R71" s="1" t="inlineStr"/>
+      <c r="S71" s="1" t="inlineStr"/>
+      <c r="T71" s="1" t="inlineStr"/>
+      <c r="U71" s="1" t="inlineStr"/>
+      <c r="V71" s="1" t="inlineStr"/>
+      <c r="W71" s="1" t="inlineStr"/>
+      <c r="X71" s="1" t="inlineStr"/>
+      <c r="Y71" s="1" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr"/>
+      <c r="B72" s="1" t="inlineStr"/>
+      <c r="C72" s="1" t="inlineStr"/>
+      <c r="D72" s="1" t="inlineStr"/>
+      <c r="E72" s="1" t="inlineStr"/>
+      <c r="F72" s="1" t="inlineStr"/>
+      <c r="G72" s="1" t="inlineStr"/>
+      <c r="H72" s="1" t="inlineStr"/>
+      <c r="I72" s="1" t="inlineStr"/>
+      <c r="J72" s="1" t="inlineStr"/>
+      <c r="K72" s="1" t="inlineStr"/>
+      <c r="L72" s="1" t="inlineStr"/>
+      <c r="M72" s="1" t="inlineStr"/>
+      <c r="N72" s="1" t="inlineStr">
+        <is>
+          <t>L180: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O72" s="1" t="inlineStr"/>
+      <c r="P72" s="1" t="inlineStr"/>
+      <c r="Q72" s="1" t="inlineStr"/>
+      <c r="R72" s="1" t="inlineStr"/>
+      <c r="S72" s="1" t="inlineStr"/>
+      <c r="T72" s="1" t="inlineStr"/>
+      <c r="U72" s="1" t="inlineStr"/>
+      <c r="V72" s="1" t="inlineStr"/>
+      <c r="W72" s="1" t="inlineStr"/>
+      <c r="X72" s="1" t="inlineStr"/>
+      <c r="Y72" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
